--- a/Output_2026/SAAM_Part1_EUR_template.xlsx
+++ b/Output_2026/SAAM_Part1_EUR_template.xlsx
@@ -721,7 +721,7 @@
         <v>0.08185402999999999</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>0.03942931</v>
+        <v>0.04673477</v>
       </c>
       <c r="E3" s="22" t="n">
         <v>41640</v>
@@ -730,7 +730,7 @@
         <v>-0.0335015</v>
       </c>
       <c r="G3" s="24" t="n">
-        <v>0.03796384</v>
+        <v>0.03815449</v>
       </c>
     </row>
     <row r="4">
@@ -743,7 +743,7 @@
         <v>0.1586989</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>0.13920969</v>
+        <v>0.13394331</v>
       </c>
       <c r="E4" s="9" t="n">
         <v>41671</v>
@@ -752,7 +752,7 @@
         <v>0.0708743</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>0.07575729</v>
+        <v>0.07859840999999999</v>
       </c>
     </row>
     <row r="5">
@@ -765,7 +765,7 @@
         <v>0.07161478</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.03016887</v>
+        <v>0.0384301</v>
       </c>
       <c r="E5" s="9" t="n">
         <v>41699</v>
@@ -774,7 +774,7 @@
         <v>-0.00690468</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>-0.00611141</v>
+        <v>-0.00366725</v>
       </c>
     </row>
     <row r="6">
@@ -787,7 +787,7 @@
         <v>0.50660616</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.2727764</v>
+        <v>0.33804285</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>41730</v>
@@ -796,7 +796,7 @@
         <v>0.01989565</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>0.02523205</v>
+        <v>0.02577997</v>
       </c>
     </row>
     <row r="7">
@@ -809,7 +809,7 @@
         <v>-0.15341776</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.12018987</v>
+        <v>-0.12008288</v>
       </c>
       <c r="E7" s="9" t="n">
         <v>41760</v>
@@ -818,7 +818,7 @@
         <v>0.01270543</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>0.01622898</v>
+        <v>0.01585161</v>
       </c>
     </row>
     <row r="8">
@@ -831,7 +831,7 @@
         <v>0.18269875</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.14278022</v>
+        <v>0.12789702</v>
       </c>
       <c r="E8" s="9" t="n">
         <v>41791</v>
@@ -840,7 +840,7 @@
         <v>-0.00459124</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.008244720000000001</v>
+        <v>0.00707532</v>
       </c>
     </row>
     <row r="9">
@@ -866,7 +866,7 @@
         <v>-0.03910022</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.02909647</v>
+        <v>-0.02996687</v>
       </c>
     </row>
     <row r="10">
@@ -877,7 +877,7 @@
         <v>0.00522623</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.00452561</v>
+        <v>0.00507116</v>
       </c>
     </row>
     <row r="11">
@@ -888,7 +888,7 @@
         <v>-0.03344536</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.04544328</v>
+        <v>-0.04670256</v>
       </c>
     </row>
     <row r="12">
@@ -900,7 +900,7 @@
         <v>-0.02037105</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>0.04051039</v>
+        <v>0.04112383</v>
       </c>
     </row>
     <row r="13">
@@ -911,7 +911,7 @@
         <v>0.0272772</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.02558149</v>
+        <v>0.0249358</v>
       </c>
     </row>
     <row r="14">
@@ -922,7 +922,7 @@
         <v>-0.04049661</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>-0.01922815</v>
+        <v>-0.02098174</v>
       </c>
     </row>
     <row r="15">
@@ -933,7 +933,7 @@
         <v>-0.00115655</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.03267707</v>
+        <v>-0.02402906</v>
       </c>
     </row>
     <row r="16">
@@ -944,7 +944,7 @@
         <v>0.06100355</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.05425822</v>
+        <v>0.04384912</v>
       </c>
     </row>
     <row r="17">
@@ -955,7 +955,7 @@
         <v>-0.02121773</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.02104998</v>
+        <v>-0.009444950000000001</v>
       </c>
     </row>
     <row r="18">
@@ -966,7 +966,7 @@
         <v>0.03752309</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.04079696</v>
+        <v>0.04446331</v>
       </c>
     </row>
     <row r="19">
@@ -977,7 +977,7 @@
         <v>-0.00444852</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.00090475</v>
+        <v>0.0127996</v>
       </c>
     </row>
     <row r="20">
@@ -988,7 +988,7 @@
         <v>-0.02694124</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.02182154</v>
+        <v>-0.00550978</v>
       </c>
     </row>
     <row r="21">
@@ -999,7 +999,7 @@
         <v>0.03186669</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.06120899</v>
+        <v>0.06929818</v>
       </c>
     </row>
     <row r="22">
@@ -1010,7 +1010,7 @@
         <v>-0.06768982</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-0.05348502</v>
+        <v>-0.04083225</v>
       </c>
     </row>
     <row r="23">
@@ -1021,7 +1021,7 @@
         <v>-0.04502171</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.07055707</v>
+        <v>-0.05350586</v>
       </c>
     </row>
     <row r="24">
@@ -1032,7 +1032,7 @@
         <v>0.07224091000000001</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.04274497</v>
+        <v>0.04027464</v>
       </c>
     </row>
     <row r="25">
@@ -1043,7 +1043,7 @@
         <v>-0.01693822</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0.00430477</v>
+        <v>0.00021303</v>
       </c>
     </row>
     <row r="26">
@@ -1054,7 +1054,7 @@
         <v>-0.02612204</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.00183985</v>
+        <v>0.01760319</v>
       </c>
     </row>
     <row r="27">
@@ -1065,7 +1065,7 @@
         <v>-0.06556903</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>-0.0493841</v>
+        <v>-0.04710673</v>
       </c>
     </row>
     <row r="28">
@@ -1076,7 +1076,7 @@
         <v>-0.02161857</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>-0.04541031</v>
+        <v>-0.0272848</v>
       </c>
     </row>
     <row r="29">
@@ -1087,7 +1087,7 @@
         <v>0.06439792</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>0.05151642</v>
+        <v>0.04657547</v>
       </c>
     </row>
     <row r="30">
@@ -1098,7 +1098,7 @@
         <v>0.02490328</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>0.01950848</v>
+        <v>-0.00644485</v>
       </c>
     </row>
     <row r="31">
@@ -1109,7 +1109,7 @@
         <v>-0.00191065</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>-0.00397532</v>
+        <v>0.01123232</v>
       </c>
     </row>
     <row r="32">
@@ -1120,7 +1120,7 @@
         <v>-0.04858814</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>-0.03084826</v>
+        <v>-0.02913914</v>
       </c>
     </row>
     <row r="33">
@@ -1131,7 +1131,7 @@
         <v>0.04064367</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.0408103</v>
+        <v>0.01849069</v>
       </c>
     </row>
     <row r="34">
@@ -1142,7 +1142,7 @@
         <v>0.00579078</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>-0.04366335</v>
+        <v>-0.02383148</v>
       </c>
     </row>
     <row r="35">
@@ -1153,7 +1153,7 @@
         <v>0.0072761</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>0.00386865</v>
+        <v>-0.00970183</v>
       </c>
     </row>
     <row r="36">
@@ -1164,7 +1164,7 @@
         <v>-0.0300432</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>-0.03769446</v>
+        <v>-0.05295308</v>
       </c>
     </row>
     <row r="37">
@@ -1175,7 +1175,7 @@
         <v>-0.02282074</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>0.00081559</v>
+        <v>-0.01892801</v>
       </c>
     </row>
     <row r="38">
@@ -1186,7 +1186,7 @@
         <v>0.05029991</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0.00332801</v>
+        <v>0.01500259</v>
       </c>
     </row>
     <row r="39">
@@ -1197,7 +1197,7 @@
         <v>0.0189369</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>-0.01338374</v>
+        <v>-0.01001732</v>
       </c>
     </row>
     <row r="40">
@@ -1208,7 +1208,7 @@
         <v>0.01137494</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0.02050699</v>
+        <v>0.02412757</v>
       </c>
     </row>
     <row r="41">
@@ -1219,7 +1219,7 @@
         <v>0.04161641</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0.00066594</v>
+        <v>0.0059994</v>
       </c>
     </row>
     <row r="42">
@@ -1230,7 +1230,7 @@
         <v>0.03933847</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>0.04048784</v>
+        <v>0.03400225</v>
       </c>
     </row>
     <row r="43">
@@ -1241,7 +1241,7 @@
         <v>0.05072624</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0.02390821</v>
+        <v>0.03872557</v>
       </c>
     </row>
     <row r="44">
@@ -1252,7 +1252,7 @@
         <v>-0.0094424</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0.00518</v>
+        <v>-0.00018995</v>
       </c>
     </row>
     <row r="45">
@@ -1263,7 +1263,7 @@
         <v>0.02720137</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>0.01304295</v>
+        <v>0.01392437</v>
       </c>
     </row>
     <row r="46">
@@ -1274,7 +1274,7 @@
         <v>-0.0011137</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>-0.07805976000000001</v>
+        <v>-0.08359084</v>
       </c>
     </row>
     <row r="47">
@@ -1285,7 +1285,7 @@
         <v>0.03506897</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0.02412614</v>
+        <v>0.02672759</v>
       </c>
     </row>
     <row r="48">
@@ -1296,7 +1296,7 @@
         <v>0.00701093</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>-0.01313596</v>
+        <v>-0.01240207</v>
       </c>
     </row>
     <row r="49">
@@ -1307,7 +1307,7 @@
         <v>0.00356959</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>-0.008688299999999999</v>
+        <v>-0.00525071</v>
       </c>
     </row>
     <row r="50">
@@ -1318,7 +1318,7 @@
         <v>0.01098816</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>0.02820717</v>
+        <v>0.0153909</v>
       </c>
     </row>
     <row r="51">
@@ -1329,7 +1329,7 @@
         <v>0.05564212</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.02436682</v>
+        <v>0.02760979</v>
       </c>
     </row>
     <row r="52">
@@ -1340,7 +1340,7 @@
         <v>-0.05842843</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>-0.04102375</v>
+        <v>-0.03979227</v>
       </c>
     </row>
     <row r="53">
@@ -1351,7 +1351,7 @@
         <v>-0.01101782</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>-0.00465594</v>
+        <v>-0.00486839</v>
       </c>
     </row>
     <row r="54">
@@ -1362,7 +1362,7 @@
         <v>0.02812416</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.01688156</v>
+        <v>0.01975567</v>
       </c>
     </row>
     <row r="55">
@@ -1373,7 +1373,7 @@
         <v>-0.03046158</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.01378583</v>
+        <v>0.00316307</v>
       </c>
     </row>
     <row r="56">
@@ -1384,7 +1384,7 @@
         <v>-0.00394049</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.01299949</v>
+        <v>0.00809496</v>
       </c>
     </row>
     <row r="57">
@@ -1395,7 +1395,7 @@
         <v>0.03200097</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>0.016745</v>
+        <v>0.01346476</v>
       </c>
     </row>
     <row r="58">
@@ -1406,7 +1406,7 @@
         <v>-0.02603123</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-0.00178017</v>
+        <v>0.0039027</v>
       </c>
     </row>
     <row r="59">
@@ -1417,7 +1417,7 @@
         <v>0.00372612</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-0.008073240000000001</v>
+        <v>-0.01293089</v>
       </c>
     </row>
     <row r="60">
@@ -1428,7 +1428,7 @@
         <v>-0.07619581</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-0.02203078</v>
+        <v>-0.02631293</v>
       </c>
     </row>
     <row r="61">
@@ -1439,7 +1439,7 @@
         <v>-0.00379871</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>0.00901829</v>
+        <v>0.01593968</v>
       </c>
     </row>
     <row r="62">
@@ -1450,7 +1450,7 @@
         <v>-0.05148098</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-0.07294615</v>
+        <v>-0.07573135</v>
       </c>
     </row>
     <row r="63">
@@ -1461,7 +1461,7 @@
         <v>0.06903848</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>0.06209884</v>
+        <v>0.06008206</v>
       </c>
     </row>
     <row r="64">
@@ -1472,7 +1472,7 @@
         <v>0.03412629</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>0.02688153</v>
+        <v>0.03012607</v>
       </c>
     </row>
     <row r="65">
@@ -1483,7 +1483,7 @@
         <v>0.0091938</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>0.02259234</v>
+        <v>0.02056212</v>
       </c>
     </row>
     <row r="66">
@@ -1494,7 +1494,7 @@
         <v>0.03836692</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-0.00631842</v>
+        <v>-0.00409113</v>
       </c>
     </row>
     <row r="67">
@@ -1505,7 +1505,7 @@
         <v>-0.0530067</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-0.0391123</v>
+        <v>-0.02985205</v>
       </c>
     </row>
     <row r="68">
@@ -1516,7 +1516,7 @@
         <v>0.06779359</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>0.03832587</v>
+        <v>0.03800441</v>
       </c>
     </row>
     <row r="69">
@@ -1527,7 +1527,7 @@
         <v>-0.01647681</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-0.02654509</v>
+        <v>-0.0191011</v>
       </c>
     </row>
     <row r="70">
@@ -1538,7 +1538,7 @@
         <v>-0.02338625</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-0.02852016</v>
+        <v>-0.01391106</v>
       </c>
     </row>
     <row r="71">
@@ -1549,7 +1549,7 @@
         <v>0.02811969</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>0.00164852</v>
+        <v>0.00132248</v>
       </c>
     </row>
     <row r="72">
@@ -1560,7 +1560,7 @@
         <v>0.03087978</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>0.009454550000000001</v>
+        <v>0.01518124</v>
       </c>
     </row>
     <row r="73">
@@ -1571,7 +1571,7 @@
         <v>0.01647657</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>0.02353685</v>
+        <v>0.01925387</v>
       </c>
     </row>
     <row r="74">
@@ -1582,7 +1582,7 @@
         <v>0.04035406</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>0.05699041</v>
+        <v>0.05226576</v>
       </c>
     </row>
     <row r="75">
@@ -1593,7 +1593,7 @@
         <v>-0.02688241</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>-0.00340182</v>
+        <v>-0.00314853</v>
       </c>
     </row>
     <row r="76">
@@ -1604,7 +1604,7 @@
         <v>-0.09437592</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>-0.07518068</v>
+        <v>-0.07319808999999999</v>
       </c>
     </row>
     <row r="77">
@@ -1615,7 +1615,7 @@
         <v>-0.15341776</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>-0.1196924</v>
+        <v>-0.10151412</v>
       </c>
     </row>
     <row r="78">
@@ -1626,7 +1626,7 @@
         <v>0.0626791</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>0.06814394</v>
+        <v>0.05832865</v>
       </c>
     </row>
     <row r="79">
@@ -1637,7 +1637,7 @@
         <v>0.04444673</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>0.02860375</v>
+        <v>0.02642231</v>
       </c>
     </row>
     <row r="80">
@@ -1648,7 +1648,7 @@
         <v>0.04065667</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>0.00305805</v>
+        <v>0.00416726</v>
       </c>
     </row>
     <row r="81">
@@ -1659,7 +1659,7 @@
         <v>0.03507883</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>0.04527499</v>
+        <v>0.04316416</v>
       </c>
     </row>
     <row r="82">
@@ -1670,7 +1670,7 @@
         <v>0.04453689</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>0.03568406</v>
+        <v>0.03215971</v>
       </c>
     </row>
     <row r="83">
@@ -1681,7 +1681,7 @@
         <v>-0.03752093</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>-0.05394934</v>
+        <v>-0.05368043</v>
       </c>
     </row>
     <row r="84">
@@ -1692,7 +1692,7 @@
         <v>-0.05223892</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>-0.02979716</v>
+        <v>-0.02800217</v>
       </c>
     </row>
     <row r="85">
@@ -1703,7 +1703,7 @@
         <v>0.18269875</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>0.14278022</v>
+        <v>0.12789702</v>
       </c>
     </row>
     <row r="86">
@@ -1714,7 +1714,7 @@
         <v>0.04549735</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>0.04457488</v>
+        <v>0.04463808</v>
       </c>
     </row>
     <row r="87">
@@ -1725,7 +1725,7 @@
         <v>-0.02019327</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>-0.00794052</v>
+        <v>-0.01090865</v>
       </c>
     </row>
     <row r="88">
@@ -1736,7 +1736,7 @@
         <v>0.03477731</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>-0.01518732</v>
+        <v>-0.01093814</v>
       </c>
     </row>
     <row r="89">
@@ -1747,7 +1747,7 @@
         <v>0.03548203</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>0.01904627</v>
+        <v>0.01672886</v>
       </c>
     </row>
     <row r="90">
@@ -1758,7 +1758,7 @@
         <v>0.05412212</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>0.03487392</v>
+        <v>0.03673268</v>
       </c>
     </row>
     <row r="91">
@@ -1769,7 +1769,7 @@
         <v>0.04580791</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>0.01806173</v>
+        <v>0.02012106</v>
       </c>
     </row>
     <row r="92">
@@ -1780,7 +1780,7 @@
         <v>-0.01653437</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>-0.01328241</v>
+        <v>-0.011668</v>
       </c>
     </row>
     <row r="93">
@@ -1791,7 +1791,7 @@
         <v>0.01707257</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>0.04388201</v>
+        <v>0.04480016</v>
       </c>
     </row>
     <row r="94">
@@ -1802,7 +1802,7 @@
         <v>0.01408531</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>0.01242333</v>
+        <v>0.01405376</v>
       </c>
     </row>
     <row r="95">
@@ -1813,7 +1813,7 @@
         <v>-0.04596834</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>-0.06260117</v>
+        <v>-0.06627503</v>
       </c>
     </row>
     <row r="96">
@@ -1824,7 +1824,7 @@
         <v>0.04652986</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>0.02432789</v>
+        <v>0.02850233</v>
       </c>
     </row>
     <row r="97">
@@ -1835,7 +1835,7 @@
         <v>-0.04823199</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>-0.01601348</v>
+        <v>-0.01667193</v>
       </c>
     </row>
     <row r="98">
@@ -1846,7 +1846,7 @@
         <v>0.06732629</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>0.05035537</v>
+        <v>0.05007695</v>
       </c>
     </row>
     <row r="99">
@@ -1857,7 +1857,7 @@
         <v>-0.0422441</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>-0.04496932</v>
+        <v>-0.03905338</v>
       </c>
     </row>
     <row r="100">
@@ -1868,7 +1868,7 @@
         <v>-0.03447408</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>0.0036281</v>
+        <v>0.00508334</v>
       </c>
     </row>
     <row r="101">
@@ -1879,7 +1879,7 @@
         <v>0.00504886</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.02245375</v>
+        <v>0.02507589</v>
       </c>
     </row>
     <row r="102">
@@ -1890,7 +1890,7 @@
         <v>-0.05871224</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>-0.03378285</v>
+        <v>-0.03244454</v>
       </c>
     </row>
     <row r="103">
@@ -1901,7 +1901,7 @@
         <v>0.00986357</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>-0.00169236</v>
+        <v>-0.00206499</v>
       </c>
     </row>
     <row r="104">
@@ -1912,7 +1912,7 @@
         <v>-0.09907642</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>-0.06650362999999999</v>
+        <v>-0.06955583999999999</v>
       </c>
     </row>
     <row r="105">
@@ -1923,7 +1923,7 @@
         <v>0.05138003</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>0.03433606</v>
+        <v>0.0333702</v>
       </c>
     </row>
     <row r="106">
@@ -1934,7 +1934,7 @@
         <v>-0.05769612</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>-0.04483574</v>
+        <v>-0.04441808</v>
       </c>
     </row>
     <row r="107">
@@ -1945,7 +1945,7 @@
         <v>-0.08909882</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>-0.12018987</v>
+        <v>-0.12008288</v>
       </c>
     </row>
     <row r="108">
@@ -1956,7 +1956,7 @@
         <v>0.07742585</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>0.08011983</v>
+        <v>0.07755742</v>
       </c>
     </row>
     <row r="109">
@@ -1967,7 +1967,7 @@
         <v>0.10967048</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>0.09285317999999999</v>
+        <v>0.08959122999999999</v>
       </c>
     </row>
     <row r="110">
@@ -1978,7 +1978,7 @@
         <v>-0.0084805</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>0.00447944</v>
+        <v>0.00485238</v>
       </c>
     </row>
     <row r="111">
@@ -1989,7 +1989,7 @@
         <v>0.09136865</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>0.00051659</v>
+        <v>0.00266241</v>
       </c>
     </row>
     <row r="112">
@@ -2000,7 +2000,7 @@
         <v>-0.00458824</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>-0.01175882</v>
+        <v>-0.00906991</v>
       </c>
     </row>
     <row r="113">
@@ -2011,7 +2011,7 @@
         <v>0.02553789</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>0.00695096</v>
+        <v>0.01092833</v>
       </c>
     </row>
     <row r="114">
@@ -2022,7 +2022,7 @@
         <v>0.04135268</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>0.04409493</v>
+        <v>0.04810151</v>
       </c>
     </row>
     <row r="115">
@@ -2033,7 +2033,7 @@
         <v>-0.06038681</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>-0.04069544</v>
+        <v>-0.03976323</v>
       </c>
     </row>
     <row r="116">
@@ -2044,7 +2044,7 @@
         <v>0.05285053</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>-0.10259647</v>
+        <v>-0.10843862</v>
       </c>
     </row>
     <row r="117">
@@ -2055,7 +2055,7 @@
         <v>0.02673463</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>0.03402175</v>
+        <v>0.03432904</v>
       </c>
     </row>
     <row r="118">
@@ -2066,7 +2066,7 @@
         <v>-0.0373647</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>-0.03306774</v>
+        <v>-0.0329143</v>
       </c>
     </row>
     <row r="119">
@@ -2077,7 +2077,7 @@
         <v>-0.04000682</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>-0.03159579</v>
+        <v>-0.03299869</v>
       </c>
     </row>
     <row r="120">
@@ -2088,7 +2088,7 @@
         <v>-0.03672507</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>-0.02060311</v>
+        <v>-0.01636109</v>
       </c>
     </row>
     <row r="121">
@@ -2099,7 +2099,7 @@
         <v>0.09876596</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>0.04298923</v>
+        <v>0.04137376</v>
       </c>
     </row>
     <row r="122">
@@ -2110,7 +2110,7 @@
         <v>0.05031398</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>0.03788094</v>
+        <v>0.03481093</v>
       </c>
     </row>
     <row r="123">
@@ -2121,7 +2121,7 @@
         <v>-0.00237811</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>-0.00715738</v>
+        <v>-0.0059309</v>
       </c>
     </row>
     <row r="124">
@@ -2132,7 +2132,7 @@
         <v>0.0190667</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>0.00098565</v>
+        <v>-0.00077377</v>
       </c>
     </row>
     <row r="125">
@@ -2143,7 +2143,7 @@
         <v>0.03380657</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>0.02797657</v>
+        <v>0.02621055</v>
       </c>
     </row>
     <row r="126">
@@ -2154,7 +2154,7 @@
         <v>-0.02364783</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>0.01520387</v>
+        <v>0.01238063</v>
       </c>
     </row>
     <row r="127">
@@ -2165,7 +2165,7 @@
         <v>0.04528063</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>0.0427588</v>
+        <v>0.04125062</v>
       </c>
     </row>
     <row r="128">
@@ -2176,7 +2176,7 @@
         <v>-0.02945142</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>-0.02266102</v>
+        <v>-0.01750117</v>
       </c>
     </row>
     <row r="129">
@@ -2187,7 +2187,7 @@
         <v>0.02568925</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>0.0497961</v>
+        <v>0.05229416</v>
       </c>
     </row>
     <row r="130">
@@ -2198,7 +2198,7 @@
         <v>0.03738605</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>0.02593633</v>
+        <v>0.02588393</v>
       </c>
     </row>
     <row r="131">
@@ -2209,7 +2209,7 @@
         <v>0.01169918</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>-0.01005991</v>
+        <v>-0.0061087</v>
       </c>
     </row>
     <row r="132">
@@ -2220,7 +2220,7 @@
         <v>-0.05806292</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>-0.01874245</v>
+        <v>-0.02821535</v>
       </c>
     </row>
     <row r="133">
@@ -2231,7 +2231,7 @@
         <v>-0.0103714</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>-0.02373564</v>
+        <v>-0.02557112</v>
       </c>
     </row>
     <row r="134">
@@ -2242,7 +2242,7 @@
         <v>-0.01620765</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>-0.02169762</v>
+        <v>-0.02064114</v>
       </c>
     </row>
     <row r="135">
@@ -2253,7 +2253,7 @@
         <v>0.06892747</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>0.03877114</v>
+        <v>0.03712762</v>
       </c>
     </row>
     <row r="136">
@@ -2264,7 +2264,7 @@
         <v>0.03117153</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>0.00895135</v>
+        <v>0.00653427</v>
       </c>
     </row>
     <row r="137">
@@ -2275,7 +2275,7 @@
         <v>0.00111095</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>0.01749825</v>
+        <v>0.02124322</v>
       </c>
     </row>
     <row r="138">
@@ -2286,7 +2286,7 @@
         <v>0.04142947</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>0.09318882000000001</v>
+        <v>0.09246487</v>
       </c>
     </row>
     <row r="139">
@@ -2297,7 +2297,7 @@
         <v>0.04550852</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>-0.00309305</v>
+        <v>-0.00029331</v>
       </c>
     </row>
     <row r="140">
@@ -2308,7 +2308,7 @@
         <v>0.01993113</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>0.008230329999999999</v>
+        <v>0.00847798</v>
       </c>
     </row>
     <row r="141">
@@ -2319,7 +2319,7 @@
         <v>-0.01081338</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>-0.02508032</v>
+        <v>-0.02620226</v>
       </c>
     </row>
     <row r="142">
@@ -2330,7 +2330,7 @@
         <v>0.03094371</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>0.02215197</v>
+        <v>0.02305718</v>
       </c>
     </row>
     <row r="143">
@@ -2341,7 +2341,7 @@
         <v>0.02158023</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>0.00318799</v>
+        <v>0.00250008</v>
       </c>
     </row>
     <row r="144">
@@ -2352,7 +2352,7 @@
         <v>0.01028982</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>-0.01198273</v>
+        <v>-0.01152477</v>
       </c>
     </row>
     <row r="145">
@@ -2363,7 +2363,7 @@
         <v>0.0168597</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>0.01260473</v>
+        <v>0.01549763</v>
       </c>
     </row>
     <row r="146">
@@ -2374,7 +2374,7 @@
         <v>0.0372857</v>
       </c>
       <c r="G146" s="5" t="n">
-        <v>0.05284948</v>
+        <v>0.05035149</v>
       </c>
     </row>
   </sheetData>

--- a/Output_2026/SAAM_Part1_EUR_template.xlsx
+++ b/Output_2026/SAAM_Part1_EUR_template.xlsx
@@ -784,10 +784,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.50660616</v>
+        <v>0.40551025</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.33804285</v>
+        <v>0.21826224</v>
       </c>
       <c r="E6" s="9" t="n">
         <v>41730</v>
